--- a/excel/testdata/schema_header_2row/2-row-horizontal-merge-repeated/workbook.xlsx
+++ b/excel/testdata/schema_header_2row/2-row-horizontal-merge-repeated/workbook.xlsx
@@ -121,15 +121,20 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -137,12 +142,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9E9E9E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,105 +439,109 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>30</v>
       </c>
     </row>

--- a/excel/testdata/schema_header_2row/2-row-horizontal-merge-repeated/workbook.xlsx
+++ b/excel/testdata/schema_header_2row/2-row-horizontal-merge-repeated/workbook.xlsx
@@ -115,10 +115,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
